--- a/backend/data/financials_by_company/15B.F.xlsx
+++ b/backend/data/financials_by_company/15B.F.xlsx
@@ -4151,10 +4151,8 @@
           <t>Palembang</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>30258</t>
-        </is>
+      <c r="D2" t="n">
+        <v>30258</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4277,7 +4275,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>Infinity</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AK2" t="n">
